--- a/artfynd/A 15285-2022 artfynd.xlsx
+++ b/artfynd/A 15285-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 15285-2022 artfynd.xlsx
+++ b/artfynd/A 15285-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY19"/>
+  <dimension ref="A1:AY23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>74825551</v>
+        <v>82122429</v>
       </c>
       <c r="B2" t="n">
-        <v>90008</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96554</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,37 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6031</v>
+        <v>210</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Skog vid Stortrön, Srm</t>
+          <t>Ehrendals kvarn, SV, Srm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>631332.1126104206</v>
+        <v>631252</v>
       </c>
       <c r="R2" t="n">
-        <v>6539505.035521965</v>
+        <v>6539437</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,22 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2018-09-20</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-10-12</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2018-09-20</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-10-12</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,62 +760,57 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Markus Forsberg</t>
+          <t>Ralf Lundmark</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Markus Forsberg</t>
+          <t>Ralf Lundmark</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>74825538</v>
+        <v>81252101</v>
       </c>
       <c r="B3" t="n">
-        <v>90319</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92699</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4769</v>
+        <v>366</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Kandelabersvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Artomyces pyxidatus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(Pers.) Jülich</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Skog vid Stortrön, Srm</t>
+          <t>Sydväst Hedsjön, Srm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>631162.8569992069</v>
+        <v>631210</v>
       </c>
       <c r="R3" t="n">
-        <v>6539315.049322878</v>
+        <v>6539455</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -857,22 +837,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2018-09-20</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-09-11</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2018-09-20</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-09-11</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,53 +869,48 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>81252097</v>
+        <v>82122427</v>
       </c>
       <c r="B4" t="n">
-        <v>90319</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96460</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4769</v>
+        <v>771</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Platt spretmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Herzogiella turfacea</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(Lindb.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Sydväst Hedsjön, Srm</t>
+          <t>Ehrendals kvarn, SV, Srm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>631162.7574593504</v>
+        <v>631252</v>
       </c>
       <c r="R4" t="n">
-        <v>6539333.105487789</v>
+        <v>6539437</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -969,22 +934,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2019-09-11</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-10-12</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2019-09-11</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-10-12</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -999,74 +954,60 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Markus Forsberg</t>
+          <t>Ralf Lundmark</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Markus Forsberg</t>
+          <t>Ralf Lundmark</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>81252100</v>
+        <v>82122424</v>
       </c>
       <c r="B5" t="n">
-        <v>90665</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92147</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4366</v>
+        <v>1101</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Gropticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Postia guttulata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Banker</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Peck) Jülich</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Sydväst Hedsjön, Srm</t>
+          <t>Ehrendals kvarn, SV, Srm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>631158.8678224121</v>
+        <v>631169</v>
       </c>
       <c r="R5" t="n">
-        <v>6539356.192007685</v>
+        <v>6539436</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1090,22 +1031,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2019-09-11</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-10-12</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2019-09-11</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-10-12</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1120,71 +1051,57 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Markus Forsberg</t>
+          <t>Ralf Lundmark</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Markus Forsberg</t>
+          <t>Ralf Lundmark</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>81252098</v>
+        <v>92817931</v>
       </c>
       <c r="B6" t="n">
-        <v>90665</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4366</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Banker</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Sydväst Hedsjön, Srm</t>
+          <t>Väster om blivande NR Ehrendal Södra, Srm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>631162.8690652726</v>
+        <v>631276</v>
       </c>
       <c r="R6" t="n">
-        <v>6539344.976965214</v>
+        <v>6539459</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1211,22 +1128,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2019-09-11</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-03-23</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2019-09-11</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-03-23</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1241,65 +1148,60 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Markus Forsberg</t>
+          <t>Amanda Lidén</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Markus Forsberg</t>
+          <t>Amanda Lidén</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>81252101</v>
+        <v>82122428</v>
       </c>
       <c r="B7" t="n">
-        <v>90138</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97394</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>366</v>
+        <v>2590</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kandelabersvamp</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Artomyces pyxidatus</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Pers.) Jülich</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Sydväst Hedsjön, Srm</t>
+          <t>Ehrendals kvarn, SV, Srm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>631209.770624463</v>
+        <v>631252</v>
       </c>
       <c r="R7" t="n">
-        <v>6539454.933857335</v>
+        <v>6539437</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1323,22 +1225,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2019-09-11</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-10-12</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2019-09-11</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-10-12</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1353,49 +1245,44 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Markus Forsberg</t>
+          <t>Ralf Lundmark</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Markus Forsberg</t>
+          <t>Ralf Lundmark</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>82122427</v>
+        <v>82122425</v>
       </c>
       <c r="B8" t="n">
-        <v>93160</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92632</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>771</v>
+        <v>3298</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Platt spretmossa</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Herzogiella turfacea</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Lindb.) Z.Iwats.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1405,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>631251.7254750005</v>
+        <v>631191</v>
       </c>
       <c r="R8" t="n">
-        <v>6539437.276068645</v>
+        <v>6539441</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1438,19 +1325,9 @@
           <t>2019-10-12</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2019-10-12</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1477,53 +1354,57 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>82122428</v>
+        <v>81252098</v>
       </c>
       <c r="B9" t="n">
-        <v>94160</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93209</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2590</v>
+        <v>4366</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Ehrendals kvarn, SV, Srm</t>
+          <t>Sydväst Hedsjön, Srm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>631251.7254750005</v>
+        <v>631163</v>
       </c>
       <c r="R9" t="n">
-        <v>6539437.276068645</v>
+        <v>6539345</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1547,22 +1428,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2019-10-12</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-09-11</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2019-10-12</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-09-11</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1577,65 +1448,69 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Ralf Lundmark</t>
+          <t>Markus Forsberg</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Ralf Lundmark</t>
+          <t>Markus Forsberg</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>82122433</v>
+        <v>81252100</v>
       </c>
       <c r="B10" t="n">
-        <v>5113</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93209</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100526</v>
+        <v>4366</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Ehrendals kvarn, SV, Srm</t>
+          <t>Sydväst Hedsjön, Srm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>631329.0325153479</v>
+        <v>631159</v>
       </c>
       <c r="R10" t="n">
-        <v>6539504.414258726</v>
+        <v>6539356</v>
       </c>
       <c r="S10" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1659,22 +1534,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2019-10-12</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-09-11</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2019-10-12</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-09-11</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1689,27 +1554,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Ralf Lundmark</t>
+          <t>Markus Forsberg</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Ralf Lundmark</t>
+          <t>Markus Forsberg</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>82122434</v>
+        <v>82122423</v>
       </c>
       <c r="B11" t="n">
-        <v>90676</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93215</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1717,21 +1577,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5966</v>
+        <v>4368</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1741,10 +1601,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>631329.0325153479</v>
+        <v>631166</v>
       </c>
       <c r="R11" t="n">
-        <v>6539504.414258726</v>
+        <v>6539369</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1774,19 +1634,9 @@
           <t>2019-10-12</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2019-10-12</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1813,53 +1663,48 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>82122424</v>
+        <v>74825538</v>
       </c>
       <c r="B12" t="n">
-        <v>89608</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92869</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1101</v>
+        <v>4769</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gropticka</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Postia guttulata</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Peck) Jülich</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Ehrendals kvarn, SV, Srm</t>
+          <t>Skog vid Stortrön, Srm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>631168.5316490928</v>
+        <v>631163</v>
       </c>
       <c r="R12" t="n">
-        <v>6539436.498521719</v>
+        <v>6539315</v>
       </c>
       <c r="S12" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1883,22 +1728,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2019-10-12</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2018-09-20</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2019-10-12</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2018-09-20</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1913,27 +1748,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Ralf Lundmark</t>
+          <t>Markus Forsberg</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Ralf Lundmark</t>
+          <t>Markus Forsberg</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>82122429</v>
+        <v>81252097</v>
       </c>
       <c r="B13" t="n">
-        <v>93235</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92869</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1941,37 +1771,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>210</v>
+        <v>4769</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Ehrendals kvarn, SV, Srm</t>
+          <t>Sydväst Hedsjön, Srm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>631251.7254750005</v>
+        <v>631163</v>
       </c>
       <c r="R13" t="n">
-        <v>6539437.276068645</v>
+        <v>6539333</v>
       </c>
       <c r="S13" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1995,22 +1825,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2019-10-12</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-09-11</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2019-10-12</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-09-11</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2025,49 +1845,44 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Ralf Lundmark</t>
+          <t>Markus Forsberg</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Ralf Lundmark</t>
+          <t>Markus Forsberg</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>82122423</v>
+        <v>82122422</v>
       </c>
       <c r="B14" t="n">
-        <v>90671</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92905</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4368</v>
+        <v>4786</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Mandelriska</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Lactifluus volemus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>(Fr.) Kuntze</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2077,10 +1892,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>631165.6561917486</v>
+        <v>631164</v>
       </c>
       <c r="R14" t="n">
-        <v>6539369.323328904</v>
+        <v>6539334</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2110,19 +1925,9 @@
           <t>2019-10-12</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2019-10-12</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2149,53 +1954,48 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>82122432</v>
+        <v>81252103</v>
       </c>
       <c r="B15" t="n">
-        <v>5135</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>105930</v>
+        <v>5442</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Ehrendals kvarn, SV, Srm</t>
+          <t>Sydväst Hedsjön, Srm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>631329.0325153479</v>
+        <v>631305</v>
       </c>
       <c r="R15" t="n">
-        <v>6539504.414258726</v>
+        <v>6539416</v>
       </c>
       <c r="S15" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2219,22 +2019,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2019-10-12</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-09-11</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2019-10-12</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-09-11</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2249,65 +2039,60 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Ralf Lundmark</t>
+          <t>Markus Forsberg</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Ralf Lundmark</t>
+          <t>Markus Forsberg</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>82122422</v>
+        <v>81252113</v>
       </c>
       <c r="B16" t="n">
-        <v>90337</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4786</v>
+        <v>5442</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Mandelriska</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lactarius volemus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Ehrendals kvarn, SV, Srm</t>
+          <t>Sydväst Hedsjön, Srm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>631164.2711926748</v>
+        <v>631399</v>
       </c>
       <c r="R16" t="n">
-        <v>6539334.189140758</v>
+        <v>6539635</v>
       </c>
       <c r="S16" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2331,22 +2116,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2019-10-12</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-09-11</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2019-10-12</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-09-11</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2361,49 +2136,44 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Ralf Lundmark</t>
+          <t>Markus Forsberg</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Ralf Lundmark</t>
+          <t>Markus Forsberg</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>82122425</v>
+        <v>82122434</v>
       </c>
       <c r="B17" t="n">
-        <v>90074</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93235</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>3298</v>
+        <v>5966</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2413,10 +2183,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>631190.5915140953</v>
+        <v>631329</v>
       </c>
       <c r="R17" t="n">
-        <v>6539441.379568242</v>
+        <v>6539504</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2446,19 +2216,9 @@
           <t>2019-10-12</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2019-10-12</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2485,15 +2245,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>82122426</v>
+        <v>82122440</v>
       </c>
       <c r="B18" t="n">
-        <v>89777</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93235</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2501,32 +2256,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6040186</v>
+        <v>5966</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Ehrendals kvarn, SV, Srm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>631264.7328761151</v>
+        <v>631428</v>
       </c>
       <c r="R18" t="n">
-        <v>6539419.661378805</v>
+        <v>6539598</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2556,33 +2313,17 @@
           <t>2019-10-12</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2019-10-12</t>
         </is>
       </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2601,50 +2342,45 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>92817931</v>
+        <v>74825551</v>
       </c>
       <c r="B19" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92567</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1202</v>
+        <v>6031</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Wulfen:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Väster om blivande NR Ehrendal Södra, Srm</t>
+          <t>Skog vid Stortrön, Srm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>631275.7855551137</v>
+        <v>631332</v>
       </c>
       <c r="R19" t="n">
-        <v>6539459.253020174</v>
+        <v>6539505</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2671,22 +2407,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2021-03-23</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2018-09-20</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2021-03-23</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2018-09-20</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2701,15 +2427,412 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Amanda Lidén</t>
+          <t>Markus Forsberg</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Amanda Lidén</t>
+          <t>Markus Forsberg</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>82122431</v>
+      </c>
+      <c r="B20" t="n">
+        <v>92567</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>6031</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Blomkålssvamp</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Sparassis crispa</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Wulfen:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Ehrendals kvarn, SV, Srm</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>631298</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6539455</v>
+      </c>
+      <c r="S20" t="n">
+        <v>5</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Gnesta</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Frustuna</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2019-10-12</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2019-10-12</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Ralf Lundmark</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Ralf Lundmark</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>82122433</v>
+      </c>
+      <c r="B21" t="n">
+        <v>5179</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Ehrendals kvarn, SV, Srm</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>631329</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6539504</v>
+      </c>
+      <c r="S21" t="n">
+        <v>5</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Gnesta</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Frustuna</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2019-10-12</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2019-10-12</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Ralf Lundmark</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Ralf Lundmark</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>82122432</v>
+      </c>
+      <c r="B22" t="n">
+        <v>5199</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>105930</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Semanotus undatus</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Ehrendals kvarn, SV, Srm</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>631329</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6539504</v>
+      </c>
+      <c r="S22" t="n">
+        <v>5</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Gnesta</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Frustuna</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2019-10-12</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2019-10-12</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Ralf Lundmark</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Ralf Lundmark</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>82122426</v>
+      </c>
+      <c r="B23" t="n">
+        <v>92329</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>6040186</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Kötticka</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Leptoporus mollis</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Pers.:Fr.) Quél.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Ehrendals kvarn, SV, Srm</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>631265</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6539420</v>
+      </c>
+      <c r="S23" t="n">
+        <v>5</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Gnesta</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Frustuna</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2019-10-12</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2019-10-12</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF23" t="inlineStr"/>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Ralf Lundmark</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Ralf Lundmark</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 15285-2022 artfynd.xlsx
+++ b/artfynd/A 15285-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY23"/>
+  <dimension ref="A1:AZ23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82122429</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/81252101</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82122427</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82122424</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/92817931</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82122428</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1351,6 +1386,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82122425</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1457,6 +1497,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/81252098</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1563,6 +1608,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/81252100</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1660,6 +1710,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82122423</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1757,6 +1812,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74825538</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1854,6 +1914,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/81252097</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1951,6 +2016,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82122422</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2048,6 +2118,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/81252103</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2145,6 +2220,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/81252113</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2242,6 +2322,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82122434</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2339,6 +2424,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82122440</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2436,6 +2526,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74825551</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2533,6 +2628,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82122431</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2630,6 +2730,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82122433</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2727,6 +2832,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82122432</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2833,8 +2943,37 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82122426</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>